--- a/outputs/547-18.xlsx
+++ b/outputs/547-18.xlsx
@@ -132,8 +132,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -329,107 +333,107 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>1110000</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>1110000</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="C4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>1110000</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>1092666.66666667</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>17333.3333333333</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="C7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>6</v>
       </c>
     </row>
@@ -453,44 +457,44 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>1092666.66666667</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="0" t="s">
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>17333.3333333333</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
       </c>
     </row>

--- a/outputs/547-18.xlsx
+++ b/outputs/547-18.xlsx
@@ -132,12 +132,8 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -333,107 +329,107 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="17.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="0" t="n">
         <v>1110000</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="0" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="0" t="n">
         <v>1110000</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="0" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="0" t="n">
         <v>1110000</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="0" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="0" t="n">
         <v>1092666.66666667</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="0" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="0" t="n">
         <v>17333.3333333333</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="0" t="s">
         <v>6</v>
       </c>
     </row>
@@ -457,44 +453,44 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="0" t="n">
         <v>1092666.66666667</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="0" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="0" t="n">
         <v>17333.3333333333</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="0" t="s">
         <v>6</v>
       </c>
     </row>
